--- a/data/sars/keys/methods_key_final.xlsx
+++ b/data/sars/keys/methods_key_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9ACA463-41AF-2D4F-B25D-E8F2384C05D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A4D651-37E8-7842-BB19-CA1200EDF2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2200" windowWidth="28040" windowHeight="17440" xr2:uid="{FB9A1177-5406-BC4D-A72F-157AFCD7822C}"/>
+    <workbookView xWindow="5760" yWindow="4380" windowWidth="28040" windowHeight="17440" xr2:uid="{FB9A1177-5406-BC4D-A72F-157AFCD7822C}"/>
   </bookViews>
   <sheets>
     <sheet name="methods_key_final" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
   <si>
     <t>n_method_orig</t>
   </si>
@@ -194,6 +194,57 @@
   </si>
   <si>
     <t>total enumeration; capture-recapture method; discovery curve analysis; all-age count corrected for seals at sea; minimum tally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aerial survey                                                 </t>
+  </si>
+  <si>
+    <t>capture-recapture analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                    </t>
+  </si>
+  <si>
+    <t>number of dens of breeding females</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                            </t>
+  </si>
+  <si>
+    <t>shore-based census and aerial survey counts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   </t>
+  </si>
+  <si>
+    <t>shore-based census</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                            </t>
+  </si>
+  <si>
+    <t>photo-based survey methods and integrated population modelling</t>
+  </si>
+  <si>
+    <t>mixed methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                 </t>
+  </si>
+  <si>
+    <t>count (aerial and ground survey)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                              </t>
+  </si>
+  <si>
+    <t>genetic mark-recapture</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>breeding count</t>
   </si>
 </sst>
 </file>
@@ -1074,8 +1125,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B80F95-9ED1-8D49-9E7B-71D37A5E104A}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="137.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1461,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1469,12 +1524,105 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>57</v>
       </c>
       <c r="B50" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" t="s">
+        <v>36</v>
+      </c>
+      <c r="C54" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>68</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
